--- a/demo/Hausbewertung_DEMO.xlsx
+++ b/demo/Hausbewertung_DEMO.xlsx
@@ -261,7 +261,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="901">
   <si>
-    <t xml:space="preserve">Anleitung — Excel-Modell Hausbewertung Altkreis Lübbecke</t>
+    <t xml:space="preserve">Anleitung — Excel-Modell Hausbewertung NRW</t>
   </si>
   <si>
     <t xml:space="preserve">Farblegende</t>
@@ -4251,11 +4251,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="57223880"/>
-        <c:axId val="64710042"/>
+        <c:axId val="24031720"/>
+        <c:axId val="82308701"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57223880"/>
+        <c:axId val="24031720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4321,7 +4321,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64710042"/>
+        <c:crossAx val="82308701"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4329,7 +4329,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64710042"/>
+        <c:axId val="82308701"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4405,7 +4405,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57223880"/>
+        <c:crossAx val="24031720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4876,11 +4876,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="8715234"/>
-        <c:axId val="54356864"/>
+        <c:axId val="17946439"/>
+        <c:axId val="69683183"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8715234"/>
+        <c:axId val="17946439"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4946,7 +4946,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54356864"/>
+        <c:crossAx val="69683183"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4954,7 +4954,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54356864"/>
+        <c:axId val="69683183"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5030,7 +5030,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8715234"/>
+        <c:crossAx val="17946439"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5743,11 +5743,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="89354976"/>
-        <c:axId val="74472144"/>
+        <c:axId val="61063185"/>
+        <c:axId val="51548362"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89354976"/>
+        <c:axId val="61063185"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5813,7 +5813,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74472144"/>
+        <c:crossAx val="51548362"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5821,7 +5821,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74472144"/>
+        <c:axId val="51548362"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5897,7 +5897,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89354976"/>
+        <c:crossAx val="61063185"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6368,11 +6368,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="49150352"/>
-        <c:axId val="60618739"/>
+        <c:axId val="23046680"/>
+        <c:axId val="47165428"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="49150352"/>
+        <c:axId val="23046680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6438,7 +6438,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60618739"/>
+        <c:crossAx val="47165428"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6446,7 +6446,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60618739"/>
+        <c:axId val="47165428"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6522,7 +6522,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49150352"/>
+        <c:crossAx val="23046680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7235,11 +7235,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="33674580"/>
-        <c:axId val="60179099"/>
+        <c:axId val="78042335"/>
+        <c:axId val="41110367"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="33674580"/>
+        <c:axId val="78042335"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7305,7 +7305,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60179099"/>
+        <c:crossAx val="41110367"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7313,7 +7313,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60179099"/>
+        <c:axId val="41110367"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7389,7 +7389,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33674580"/>
+        <c:crossAx val="78042335"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7860,11 +7860,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="58973604"/>
-        <c:axId val="13600285"/>
+        <c:axId val="42717595"/>
+        <c:axId val="20305343"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58973604"/>
+        <c:axId val="42717595"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7930,7 +7930,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13600285"/>
+        <c:crossAx val="20305343"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7938,7 +7938,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13600285"/>
+        <c:axId val="20305343"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8014,7 +8014,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58973604"/>
+        <c:crossAx val="42717595"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
